--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/33.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/33.xlsx
@@ -426,13 +426,13 @@
         <v>-13.96209982517394</v>
       </c>
       <c r="E2">
-        <v>-7.144792885361493</v>
+        <v>-7.545377167606005</v>
       </c>
       <c r="F2">
-        <v>0.2648385359448208</v>
+        <v>-0.1609914780103687</v>
       </c>
       <c r="G2">
-        <v>-15.20478395143584</v>
+        <v>-14.19445180048782</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.76842726480698</v>
       </c>
       <c r="E3">
-        <v>-7.973453815551085</v>
+        <v>-7.047888070071355</v>
       </c>
       <c r="F3">
-        <v>0.4047043157198134</v>
+        <v>-0.07080496909679619</v>
       </c>
       <c r="G3">
-        <v>-15.15019140022049</v>
+        <v>-13.48404845430669</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.56848878903183</v>
       </c>
       <c r="E4">
-        <v>-8.919270896793115</v>
+        <v>-6.880049237925069</v>
       </c>
       <c r="F4">
-        <v>0.1948656574829597</v>
+        <v>-0.1487795216964151</v>
       </c>
       <c r="G4">
-        <v>-13.85021134367778</v>
+        <v>-13.40933606257642</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.35243711874044</v>
       </c>
       <c r="E5">
-        <v>-9.245185171125151</v>
+        <v>-7.828406793085403</v>
       </c>
       <c r="F5">
-        <v>0.3157245907138057</v>
+        <v>0.09233020169374813</v>
       </c>
       <c r="G5">
-        <v>-13.00142388340958</v>
+        <v>-12.84890042932428</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.10338641359486</v>
       </c>
       <c r="E6">
-        <v>-11.31952514592268</v>
+        <v>-10.05466801389226</v>
       </c>
       <c r="F6">
-        <v>0.9785546112085931</v>
+        <v>0.354732059264037</v>
       </c>
       <c r="G6">
-        <v>-12.90291529034303</v>
+        <v>-12.12724784940071</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.80065284626726</v>
       </c>
       <c r="E7">
-        <v>-10.84819704273034</v>
+        <v>-9.317482258657607</v>
       </c>
       <c r="F7">
-        <v>0.6757563750002324</v>
+        <v>-0.06278983345875715</v>
       </c>
       <c r="G7">
-        <v>-12.64587129249186</v>
+        <v>-12.47212062040875</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.44019726297497</v>
       </c>
       <c r="E8">
-        <v>-11.97760298871734</v>
+        <v>-11.06437733490851</v>
       </c>
       <c r="F8">
-        <v>0.7356109563683509</v>
+        <v>0.5615125813781771</v>
       </c>
       <c r="G8">
-        <v>-12.78536112878905</v>
+        <v>-11.63639988338405</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.02561401008114</v>
       </c>
       <c r="E9">
-        <v>-12.71736997413636</v>
+        <v>-11.55644132058197</v>
       </c>
       <c r="F9">
-        <v>1.101177792829239</v>
+        <v>0.8440061240446886</v>
       </c>
       <c r="G9">
-        <v>-11.36147562907528</v>
+        <v>-10.92915479764739</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.55780814079774</v>
       </c>
       <c r="E10">
-        <v>-13.09882598217247</v>
+        <v>-13.63622452113672</v>
       </c>
       <c r="F10">
-        <v>0.8967451147347375</v>
+        <v>0.3173368033357231</v>
       </c>
       <c r="G10">
-        <v>-10.73652077380828</v>
+        <v>-9.869475654891</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.05720891257154</v>
       </c>
       <c r="E11">
-        <v>-13.1301358514615</v>
+        <v>-13.72774498083174</v>
       </c>
       <c r="F11">
-        <v>1.171969447249382</v>
+        <v>0.8783947142925407</v>
       </c>
       <c r="G11">
-        <v>-10.17748550131925</v>
+        <v>-9.555678974860102</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.5405889163554</v>
       </c>
       <c r="E12">
-        <v>-14.48701157532779</v>
+        <v>-14.73852755018781</v>
       </c>
       <c r="F12">
-        <v>1.160451154126391</v>
+        <v>1.0127436545111</v>
       </c>
       <c r="G12">
-        <v>-9.998315466188355</v>
+        <v>-8.912873658045354</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.01413768358624</v>
       </c>
       <c r="E13">
-        <v>-15.69597828115554</v>
+        <v>-14.88605617640969</v>
       </c>
       <c r="F13">
-        <v>1.334489348291778</v>
+        <v>0.9189280834922979</v>
       </c>
       <c r="G13">
-        <v>-8.260560454441821</v>
+        <v>-8.192515501427641</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.49457550489978</v>
       </c>
       <c r="E14">
-        <v>-16.39629320101974</v>
+        <v>-15.9345835766197</v>
       </c>
       <c r="F14">
-        <v>1.437864168216173</v>
+        <v>0.9368207929249328</v>
       </c>
       <c r="G14">
-        <v>-8.340894152497775</v>
+        <v>-7.66887327129896</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.984161283809057</v>
       </c>
       <c r="E15">
-        <v>-17.49177181974127</v>
+        <v>-16.4160464046412</v>
       </c>
       <c r="F15">
-        <v>1.789801631568788</v>
+        <v>1.440627735038614</v>
       </c>
       <c r="G15">
-        <v>-7.463295014401298</v>
+        <v>-6.176115182186189</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.478717035081923</v>
       </c>
       <c r="E16">
-        <v>-17.81801214420186</v>
+        <v>-19.0087290997787</v>
       </c>
       <c r="F16">
-        <v>1.902135475856824</v>
+        <v>1.675817565716865</v>
       </c>
       <c r="G16">
-        <v>-6.900929333099763</v>
+        <v>-5.583487804110176</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.983620861337115</v>
       </c>
       <c r="E17">
-        <v>-18.83394811697866</v>
+        <v>-18.36919535804546</v>
       </c>
       <c r="F17">
-        <v>1.856447143902311</v>
+        <v>1.629586022633357</v>
       </c>
       <c r="G17">
-        <v>-6.129400074081533</v>
+        <v>-5.025541701103567</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.494905290393194</v>
       </c>
       <c r="E18">
-        <v>-20.05603834048064</v>
+        <v>-19.7202021795978</v>
       </c>
       <c r="F18">
-        <v>2.58172110493696</v>
+        <v>1.827481162708924</v>
       </c>
       <c r="G18">
-        <v>-5.519978298484797</v>
+        <v>-4.750077827871889</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.010745367381868</v>
       </c>
       <c r="E19">
-        <v>-21.51518512133615</v>
+        <v>-20.10686593274273</v>
       </c>
       <c r="F19">
-        <v>2.438367212883212</v>
+        <v>2.09995459804845</v>
       </c>
       <c r="G19">
-        <v>-5.503094516234514</v>
+        <v>-5.219900519168639</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.535909429245678</v>
       </c>
       <c r="E20">
-        <v>-22.33081310333167</v>
+        <v>-21.14761794308157</v>
       </c>
       <c r="F20">
-        <v>2.82888850345368</v>
+        <v>2.505663628347981</v>
       </c>
       <c r="G20">
-        <v>-4.995568021791005</v>
+        <v>-4.294725531127295</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.069168430795044</v>
       </c>
       <c r="E21">
-        <v>-22.8055013342377</v>
+        <v>-21.28872066468656</v>
       </c>
       <c r="F21">
-        <v>3.126824762501641</v>
+        <v>2.661139205478503</v>
       </c>
       <c r="G21">
-        <v>-5.460656632966597</v>
+        <v>-4.925927385826896</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.620819689183523</v>
       </c>
       <c r="E22">
-        <v>-23.14481083468442</v>
+        <v>-22.6642220021464</v>
       </c>
       <c r="F22">
-        <v>3.118089040672077</v>
+        <v>2.806783136285976</v>
       </c>
       <c r="G22">
-        <v>-5.220036251535749</v>
+        <v>-3.420182026563565</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.206755037771351</v>
       </c>
       <c r="E23">
-        <v>-23.52713630973001</v>
+        <v>-23.32422897486832</v>
       </c>
       <c r="F23">
-        <v>3.417325522276614</v>
+        <v>2.890946019750174</v>
       </c>
       <c r="G23">
-        <v>-5.611614199011823</v>
+        <v>-4.143340904707502</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.837621518598822</v>
       </c>
       <c r="E24">
-        <v>-24.09097207995104</v>
+        <v>-23.1780951186408</v>
       </c>
       <c r="F24">
-        <v>3.355640176870248</v>
+        <v>3.015924172067078</v>
       </c>
       <c r="G24">
-        <v>-4.95938706959231</v>
+        <v>-4.206820615423028</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.531289452989097</v>
       </c>
       <c r="E25">
-        <v>-24.22883694264055</v>
+        <v>-22.19065683279427</v>
       </c>
       <c r="F25">
-        <v>3.541731956758045</v>
+        <v>3.077851824478507</v>
       </c>
       <c r="G25">
-        <v>-5.849321300368112</v>
+        <v>-3.600351846447321</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.296506777482948</v>
       </c>
       <c r="E26">
-        <v>-24.03672096133915</v>
+        <v>-24.5692196914271</v>
       </c>
       <c r="F26">
-        <v>3.430924804972493</v>
+        <v>3.033139055367905</v>
       </c>
       <c r="G26">
-        <v>-5.461858360997352</v>
+        <v>-3.309030460082535</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.12747825746262</v>
       </c>
       <c r="E27">
-        <v>-24.97924131350359</v>
+        <v>-23.09902343399287</v>
       </c>
       <c r="F27">
-        <v>3.629497771179868</v>
+        <v>3.117107143004505</v>
       </c>
       <c r="G27">
-        <v>-5.018182358369767</v>
+        <v>-3.991155126267206</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.022521080627306</v>
       </c>
       <c r="E28">
-        <v>-24.19541680446395</v>
+        <v>-24.79349689513098</v>
       </c>
       <c r="F28">
-        <v>3.240924438885391</v>
+        <v>3.175632995109569</v>
       </c>
       <c r="G28">
-        <v>-5.128347382280094</v>
+        <v>-4.511152445757149</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.972419766917129</v>
       </c>
       <c r="E29">
-        <v>-23.6122082224381</v>
+        <v>-24.24690555393116</v>
       </c>
       <c r="F29">
-        <v>3.612604380179875</v>
+        <v>2.729851454031674</v>
       </c>
       <c r="G29">
-        <v>-5.635238251980063</v>
+        <v>-4.479172575847789</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.968163089917525</v>
       </c>
       <c r="E30">
-        <v>-24.48777508639914</v>
+        <v>-23.47116889946921</v>
       </c>
       <c r="F30">
-        <v>3.363121603614784</v>
+        <v>3.07180840270519</v>
       </c>
       <c r="G30">
-        <v>-5.706282559252823</v>
+        <v>-3.983199885336337</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.007006654077021</v>
       </c>
       <c r="E31">
-        <v>-23.92626242334405</v>
+        <v>-23.28890687760849</v>
       </c>
       <c r="F31">
-        <v>3.53737201437284</v>
+        <v>3.125317074470143</v>
       </c>
       <c r="G31">
-        <v>-5.277202751907883</v>
+        <v>-4.707719397696914</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.0784881027273</v>
       </c>
       <c r="E32">
-        <v>-23.52742160359249</v>
+        <v>-22.27585101430057</v>
       </c>
       <c r="F32">
-        <v>3.285757569645567</v>
+        <v>2.891839229886482</v>
       </c>
       <c r="G32">
-        <v>-5.328916783776839</v>
+        <v>-4.201911076388288</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.176226881013672</v>
       </c>
       <c r="E33">
-        <v>-22.49675903334275</v>
+        <v>-22.48726282334867</v>
       </c>
       <c r="F33">
-        <v>3.518891750045577</v>
+        <v>2.999241413953839</v>
       </c>
       <c r="G33">
-        <v>-5.554321897909197</v>
+        <v>-4.503203825917359</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.297733936449189</v>
       </c>
       <c r="E34">
-        <v>-23.09019743815192</v>
+        <v>-22.30002400855352</v>
       </c>
       <c r="F34">
-        <v>3.406565824287119</v>
+        <v>3.146877646802935</v>
       </c>
       <c r="G34">
-        <v>-5.065394048305313</v>
+        <v>-3.943009862489585</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.436031946996367</v>
       </c>
       <c r="E35">
-        <v>-22.70886822738802</v>
+        <v>-21.11558804642531</v>
       </c>
       <c r="F35">
-        <v>3.62177403743027</v>
+        <v>3.02187890630913</v>
       </c>
       <c r="G35">
-        <v>-5.203274959470419</v>
+        <v>-4.442263303630455</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.592314912635667</v>
       </c>
       <c r="E36">
-        <v>-21.92374857478218</v>
+        <v>-21.45182724149484</v>
       </c>
       <c r="F36">
-        <v>3.880101811533091</v>
+        <v>2.790889063718625</v>
       </c>
       <c r="G36">
-        <v>-5.205502956618348</v>
+        <v>-4.64137606508992</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.76582249616744</v>
       </c>
       <c r="E37">
-        <v>-20.79377656954423</v>
+        <v>-21.84350401536626</v>
       </c>
       <c r="F37">
-        <v>3.337680951789165</v>
+        <v>2.72342160801499</v>
       </c>
       <c r="G37">
-        <v>-4.628948277135496</v>
+        <v>-4.658855745537272</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.951484858439973</v>
       </c>
       <c r="E38">
-        <v>-21.25368386128922</v>
+        <v>-21.53998304500216</v>
       </c>
       <c r="F38">
-        <v>3.42073365740664</v>
+        <v>3.113868464407431</v>
       </c>
       <c r="G38">
-        <v>-5.405019604633605</v>
+        <v>-4.412902075242658</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.15177433769401</v>
       </c>
       <c r="E39">
-        <v>-19.60723033852845</v>
+        <v>-19.91183361418038</v>
       </c>
       <c r="F39">
-        <v>3.576736608607003</v>
+        <v>3.028414860622149</v>
       </c>
       <c r="G39">
-        <v>-5.08357556440699</v>
+        <v>-4.269770638852269</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.363423061496441</v>
       </c>
       <c r="E40">
-        <v>-20.85544080010667</v>
+        <v>-19.6242030591092</v>
       </c>
       <c r="F40">
-        <v>3.476527616807572</v>
+        <v>2.876952394281351</v>
       </c>
       <c r="G40">
-        <v>-4.130929669480775</v>
+        <v>-4.151107444542633</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.580698831056832</v>
       </c>
       <c r="E41">
-        <v>-19.46012738886328</v>
+        <v>-18.84517420404367</v>
       </c>
       <c r="F41">
-        <v>3.706237825018402</v>
+        <v>3.124696261751291</v>
       </c>
       <c r="G41">
-        <v>-4.667628691216341</v>
+        <v>-4.178071837959997</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.805190463556897</v>
       </c>
       <c r="E42">
-        <v>-18.77298127141339</v>
+        <v>-19.09851968240279</v>
       </c>
       <c r="F42">
-        <v>3.545749818665515</v>
+        <v>3.39051496483414</v>
       </c>
       <c r="G42">
-        <v>-4.569252519971358</v>
+        <v>-3.637767632132164</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.032745062422798</v>
       </c>
       <c r="E43">
-        <v>-18.00021982437448</v>
+        <v>-18.4638585787018</v>
       </c>
       <c r="F43">
-        <v>3.280624778773627</v>
+        <v>3.067366107612382</v>
       </c>
       <c r="G43">
-        <v>-4.978224073710764</v>
+        <v>-4.070876373398395</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.261051178909122</v>
       </c>
       <c r="E44">
-        <v>-17.26384919446121</v>
+        <v>-17.74003182178977</v>
       </c>
       <c r="F44">
-        <v>3.65172191629123</v>
+        <v>2.99200071050845</v>
       </c>
       <c r="G44">
-        <v>-4.862702587117895</v>
+        <v>-4.109063516193888</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.491986659887345</v>
       </c>
       <c r="E45">
-        <v>-16.43254363545114</v>
+        <v>-17.87962656155022</v>
       </c>
       <c r="F45">
-        <v>3.401961991190936</v>
+        <v>3.108879790773797</v>
       </c>
       <c r="G45">
-        <v>-4.651651998443818</v>
+        <v>-3.995760095112332</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.721189367774878</v>
       </c>
       <c r="E46">
-        <v>-16.85416267946128</v>
+        <v>-16.02507607271497</v>
       </c>
       <c r="F46">
-        <v>3.249797943129599</v>
+        <v>2.980932189865444</v>
       </c>
       <c r="G46">
-        <v>-4.726238589443598</v>
+        <v>-4.969616655308658</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.950020775369767</v>
       </c>
       <c r="E47">
-        <v>-16.07947663096911</v>
+        <v>-15.27980246290262</v>
       </c>
       <c r="F47">
-        <v>3.482631219405675</v>
+        <v>3.129912989036748</v>
       </c>
       <c r="G47">
-        <v>-5.03870111962217</v>
+        <v>-4.073375835280545</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.180557887648376</v>
       </c>
       <c r="E48">
-        <v>-15.62280719813961</v>
+        <v>-15.46815075382965</v>
       </c>
       <c r="F48">
-        <v>3.254446119991413</v>
+        <v>3.230478314667153</v>
       </c>
       <c r="G48">
-        <v>-5.299757498666938</v>
+        <v>-3.874021403996712</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.406115497347718</v>
       </c>
       <c r="E49">
-        <v>-14.59658706089139</v>
+        <v>-15.73902595507246</v>
       </c>
       <c r="F49">
-        <v>3.319032814634865</v>
+        <v>2.958008046739458</v>
       </c>
       <c r="G49">
-        <v>-4.967127125063127</v>
+        <v>-4.442485110181586</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.626368367942832</v>
       </c>
       <c r="E50">
-        <v>-14.59998341639714</v>
+        <v>-14.50916487017331</v>
       </c>
       <c r="F50">
-        <v>3.542541230480834</v>
+        <v>2.913632606988844</v>
       </c>
       <c r="G50">
-        <v>-5.358407123440667</v>
+        <v>-4.479321550397056</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.836639025429331</v>
       </c>
       <c r="E51">
-        <v>-13.5911662047604</v>
+        <v>-14.13804736829671</v>
       </c>
       <c r="F51">
-        <v>3.30389733720101</v>
+        <v>2.78452573335039</v>
       </c>
       <c r="G51">
-        <v>-5.394803261099415</v>
+        <v>-4.457991705487532</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.02587924734957</v>
       </c>
       <c r="E52">
-        <v>-12.52572948260576</v>
+        <v>-13.83790916801633</v>
       </c>
       <c r="F52">
-        <v>2.720024558826372</v>
+        <v>3.131191039710508</v>
       </c>
       <c r="G52">
-        <v>-5.129870233228159</v>
+        <v>-4.988168952510734</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.193990390180575</v>
       </c>
       <c r="E53">
-        <v>-12.9206033591266</v>
+        <v>-13.54699999776359</v>
       </c>
       <c r="F53">
-        <v>3.207183584356954</v>
+        <v>2.731329051650779</v>
       </c>
       <c r="G53">
-        <v>-5.895311398999667</v>
+        <v>-4.915138317914412</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.338146362479938</v>
       </c>
       <c r="E54">
-        <v>-11.40513594703769</v>
+        <v>-11.96424851886872</v>
       </c>
       <c r="F54">
-        <v>3.300044180708746</v>
+        <v>2.590461577884271</v>
       </c>
       <c r="G54">
-        <v>-5.880152410975345</v>
+        <v>-5.186665952499895</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.455470248076839</v>
       </c>
       <c r="E55">
-        <v>-10.9166539843043</v>
+        <v>-11.79017850648788</v>
       </c>
       <c r="F55">
-        <v>3.221337164123236</v>
+        <v>2.733623841522251</v>
       </c>
       <c r="G55">
-        <v>-5.227130750626407</v>
+        <v>-4.736511212251957</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.554711379071245</v>
       </c>
       <c r="E56">
-        <v>-10.92015902318623</v>
+        <v>-12.37032131161053</v>
       </c>
       <c r="F56">
-        <v>2.727599424219919</v>
+        <v>2.685713570168376</v>
       </c>
       <c r="G56">
-        <v>-5.956328063833976</v>
+        <v>-4.612739846175224</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.63762286358312</v>
       </c>
       <c r="E57">
-        <v>-10.70354399750333</v>
+        <v>-11.37521631926901</v>
       </c>
       <c r="F57">
-        <v>3.161862672174824</v>
+        <v>2.533102917038885</v>
       </c>
       <c r="G57">
-        <v>-5.78265022375273</v>
+        <v>-4.964141012986704</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.70586928040378</v>
       </c>
       <c r="E58">
-        <v>-10.19358348255155</v>
+        <v>-11.48281739016527</v>
       </c>
       <c r="F58">
-        <v>3.208010278844813</v>
+        <v>2.857647019172144</v>
       </c>
       <c r="G58">
-        <v>-6.128536021695783</v>
+        <v>-5.2214399228444</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.767438928431311</v>
       </c>
       <c r="E59">
-        <v>-9.728119753199149</v>
+        <v>-10.72720980266741</v>
       </c>
       <c r="F59">
-        <v>3.204241058766068</v>
+        <v>2.292680522016022</v>
       </c>
       <c r="G59">
-        <v>-6.201699078113677</v>
+        <v>-5.767458130273015</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.820714571221666</v>
       </c>
       <c r="E60">
-        <v>-10.06110750393117</v>
+        <v>-10.04042143466413</v>
       </c>
       <c r="F60">
-        <v>2.992350709515762</v>
+        <v>2.414496013619794</v>
       </c>
       <c r="G60">
-        <v>-6.617182474928828</v>
+        <v>-5.857263299116824</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.868150024278089</v>
       </c>
       <c r="E61">
-        <v>-9.579522407111453</v>
+        <v>-9.060835522746897</v>
       </c>
       <c r="F61">
-        <v>3.18133116899332</v>
+        <v>2.662412505034516</v>
       </c>
       <c r="G61">
-        <v>-6.236896798287209</v>
+        <v>-5.408429466539054</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.916010632101267</v>
       </c>
       <c r="E62">
-        <v>-9.203441697722445</v>
+        <v>-10.53586366194731</v>
       </c>
       <c r="F62">
-        <v>2.890887422631303</v>
+        <v>2.684932803152065</v>
       </c>
       <c r="G62">
-        <v>-6.718809601893375</v>
+        <v>-5.285558568849004</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.961497257074015</v>
       </c>
       <c r="E63">
-        <v>-9.363505139997562</v>
+        <v>-9.184748157018783</v>
       </c>
       <c r="F63">
-        <v>2.835009526816853</v>
+        <v>2.66536294915498</v>
       </c>
       <c r="G63">
-        <v>-6.40123227885663</v>
+        <v>-6.692053772844986</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.010801309993997</v>
       </c>
       <c r="E64">
-        <v>-7.897357338326191</v>
+        <v>-8.399619447464927</v>
       </c>
       <c r="F64">
-        <v>2.748357057653584</v>
+        <v>2.501294183727284</v>
       </c>
       <c r="G64">
-        <v>-6.043766192617205</v>
+        <v>-6.643594007241134</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.068999114265976</v>
       </c>
       <c r="E65">
-        <v>-8.156789085751619</v>
+        <v>-8.925511133975684</v>
       </c>
       <c r="F65">
-        <v>2.769388672210619</v>
+        <v>2.251217517443902</v>
       </c>
       <c r="G65">
-        <v>-6.379094660835523</v>
+        <v>-6.729214646523305</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.132617736428008</v>
       </c>
       <c r="E66">
-        <v>-8.21006658245186</v>
+        <v>-8.998401451603147</v>
       </c>
       <c r="F66">
-        <v>3.087746819038172</v>
+        <v>2.43341971560338</v>
       </c>
       <c r="G66">
-        <v>-6.807813618716682</v>
+        <v>-5.8798114247848</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.209406100966996</v>
       </c>
       <c r="E67">
-        <v>-8.05683207898031</v>
+        <v>-9.210329506688112</v>
       </c>
       <c r="F67">
-        <v>2.381349048809646</v>
+        <v>2.296690465393915</v>
       </c>
       <c r="G67">
-        <v>-6.991141699044902</v>
+        <v>-7.102382650255493</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.298667902963109</v>
       </c>
       <c r="E68">
-        <v>-8.077889483115978</v>
+        <v>-7.987935875427614</v>
       </c>
       <c r="F68">
-        <v>2.734903475901926</v>
+        <v>1.9581083940262</v>
       </c>
       <c r="G68">
-        <v>-6.706328845210323</v>
+        <v>-6.159380374485173</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.392020393213624</v>
       </c>
       <c r="E69">
-        <v>-7.939771025882032</v>
+        <v>-8.359963600579757</v>
       </c>
       <c r="F69">
-        <v>2.590840083598061</v>
+        <v>2.03310320394592</v>
       </c>
       <c r="G69">
-        <v>-6.590575620429706</v>
+        <v>-6.097638700177765</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.49237767103147</v>
       </c>
       <c r="E70">
-        <v>-7.47618661324281</v>
+        <v>-8.346034014532163</v>
       </c>
       <c r="F70">
-        <v>2.442411997791245</v>
+        <v>1.775768413452079</v>
       </c>
       <c r="G70">
-        <v>-6.790847072827916</v>
+        <v>-6.510576287473218</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.594114617837231</v>
       </c>
       <c r="E71">
-        <v>-7.788370554383589</v>
+        <v>-8.521775033821834</v>
       </c>
       <c r="F71">
-        <v>2.544413744686953</v>
+        <v>2.072144722173333</v>
       </c>
       <c r="G71">
-        <v>-7.100916078581595</v>
+        <v>-6.413173416616782</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.689959072982573</v>
       </c>
       <c r="E72">
-        <v>-8.378987719885981</v>
+        <v>-8.893857100662069</v>
       </c>
       <c r="F72">
-        <v>2.27095682797394</v>
+        <v>1.626150964502768</v>
       </c>
       <c r="G72">
-        <v>-6.827733171226476</v>
+        <v>-6.142168848226502</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.782635484818353</v>
       </c>
       <c r="E73">
-        <v>-7.608087475664225</v>
+        <v>-8.706613757392915</v>
       </c>
       <c r="F73">
-        <v>2.133253598626479</v>
+        <v>1.994625485024403</v>
       </c>
       <c r="G73">
-        <v>-6.598646730454449</v>
+        <v>-5.809982087724953</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.864881560321331</v>
       </c>
       <c r="E74">
-        <v>-7.508257266165131</v>
+        <v>-7.80675615885473</v>
       </c>
       <c r="F74">
-        <v>2.113488948801795</v>
+        <v>1.608492643545619</v>
       </c>
       <c r="G74">
-        <v>-6.222866706291777</v>
+        <v>-6.433457129135896</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.932574528466668</v>
       </c>
       <c r="E75">
-        <v>-8.93867993638999</v>
+        <v>-9.52681096966217</v>
       </c>
       <c r="F75">
-        <v>1.906205600059503</v>
+        <v>1.461029034641305</v>
       </c>
       <c r="G75">
-        <v>-6.276279048022379</v>
+        <v>-5.418814647895748</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.986085580463964</v>
       </c>
       <c r="E76">
-        <v>-9.264843276792448</v>
+        <v>-8.906274176391101</v>
       </c>
       <c r="F76">
-        <v>1.922896276702319</v>
+        <v>1.559275814811507</v>
       </c>
       <c r="G76">
-        <v>-6.079136061158779</v>
+        <v>-5.37624434280626</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.01540497769357</v>
       </c>
       <c r="E77">
-        <v>-8.140758287764465</v>
+        <v>-9.132285785639921</v>
       </c>
       <c r="F77">
-        <v>1.729376916071112</v>
+        <v>1.529266171419845</v>
       </c>
       <c r="G77">
-        <v>-6.686660894161514</v>
+        <v>-5.494788357476483</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.01727992019202</v>
       </c>
       <c r="E78">
-        <v>-9.113116755165452</v>
+        <v>-10.10484803437125</v>
       </c>
       <c r="F78">
-        <v>1.710065206138243</v>
+        <v>1.526220704944455</v>
       </c>
       <c r="G78">
-        <v>-6.569398060614988</v>
+        <v>-5.864632573487242</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.98932963864306</v>
       </c>
       <c r="E79">
-        <v>-9.521521712021212</v>
+        <v>-10.97062886600172</v>
       </c>
       <c r="F79">
-        <v>1.620465460266341</v>
+        <v>1.169283482016797</v>
       </c>
       <c r="G79">
-        <v>-5.573271460575985</v>
+        <v>-5.226912254620816</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.922526301420854</v>
       </c>
       <c r="E80">
-        <v>-10.81728567915398</v>
+        <v>-10.01030255403911</v>
       </c>
       <c r="F80">
-        <v>1.218181985861905</v>
+        <v>1.366784279319419</v>
       </c>
       <c r="G80">
-        <v>-6.287419033762026</v>
+        <v>-5.156146033173354</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.820748528084444</v>
       </c>
       <c r="E81">
-        <v>-10.41692782060986</v>
+        <v>-11.26312753063115</v>
       </c>
       <c r="F81">
-        <v>1.538788995089382</v>
+        <v>0.7934969912835782</v>
       </c>
       <c r="G81">
-        <v>-5.384898108845915</v>
+        <v>-4.925450667269241</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.684933578582031</v>
       </c>
       <c r="E82">
-        <v>-12.06008461429304</v>
+        <v>-12.6729411156471</v>
       </c>
       <c r="F82">
-        <v>1.127145818724699</v>
+        <v>1.091711982572657</v>
       </c>
       <c r="G82">
-        <v>-5.34222186629917</v>
+        <v>-5.027743213887182</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.510883660750347</v>
       </c>
       <c r="E83">
-        <v>-11.85076948871051</v>
+        <v>-12.84013237601029</v>
       </c>
       <c r="F83">
-        <v>1.222374055420073</v>
+        <v>1.020418293377319</v>
       </c>
       <c r="G83">
-        <v>-5.934961802923519</v>
+        <v>-4.473120898602001</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.307208287712958</v>
       </c>
       <c r="E84">
-        <v>-13.34143897713341</v>
+        <v>-13.91904130833776</v>
       </c>
       <c r="F84">
-        <v>1.0865158434641</v>
+        <v>0.8636773352203618</v>
       </c>
       <c r="G84">
-        <v>-4.936547615916878</v>
+        <v>-3.953133510748676</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.07861291215802</v>
       </c>
       <c r="E85">
-        <v>-14.55710329601851</v>
+        <v>-14.35890104565079</v>
       </c>
       <c r="F85">
-        <v>0.9393816453901983</v>
+        <v>0.5100294694790715</v>
       </c>
       <c r="G85">
-        <v>-4.815888162647061</v>
+        <v>-4.451416962046539</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.826536721971593</v>
       </c>
       <c r="E86">
-        <v>-15.82149852370015</v>
+        <v>-16.51488487833261</v>
       </c>
       <c r="F86">
-        <v>0.7419362777946161</v>
+        <v>0.5556797924916136</v>
       </c>
       <c r="G86">
-        <v>-5.342791280131925</v>
+        <v>-4.183669970466904</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.562969419806519</v>
       </c>
       <c r="E87">
-        <v>-17.29113777883143</v>
+        <v>-16.86904324505049</v>
       </c>
       <c r="F87">
-        <v>0.6961101634254603</v>
+        <v>0.5677587175086702</v>
       </c>
       <c r="G87">
-        <v>-4.358105925476642</v>
+        <v>-3.50051241407398</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.290796797786918</v>
       </c>
       <c r="E88">
-        <v>-18.33299473682814</v>
+        <v>-18.90655314074364</v>
       </c>
       <c r="F88">
-        <v>0.8459319104378629</v>
+        <v>0.6410304553923917</v>
       </c>
       <c r="G88">
-        <v>-4.390105658659238</v>
+        <v>-3.882224935843027</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.010790520285639</v>
       </c>
       <c r="E89">
-        <v>-20.25133783900944</v>
+        <v>-20.85090779762499</v>
       </c>
       <c r="F89">
-        <v>0.7337501019177096</v>
+        <v>0.3043282429463035</v>
       </c>
       <c r="G89">
-        <v>-3.882761244220389</v>
+        <v>-3.748171015321319</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.727488744836513</v>
       </c>
       <c r="E90">
-        <v>-21.39440166260357</v>
+        <v>-21.34029998363393</v>
       </c>
       <c r="F90">
-        <v>0.5555040011349998</v>
+        <v>0.8480382393053973</v>
       </c>
       <c r="G90">
-        <v>-4.429660056762449</v>
+        <v>-3.450115979329655</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.434970272884543</v>
       </c>
       <c r="E91">
-        <v>-22.77514244449028</v>
+        <v>-23.96796061200668</v>
       </c>
       <c r="F91">
-        <v>0.6161615214022461</v>
+        <v>0.3485571898997386</v>
       </c>
       <c r="G91">
-        <v>-3.669257541301711</v>
+        <v>-3.15170340441975</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.129434623024494</v>
       </c>
       <c r="E92">
-        <v>-24.75474221457333</v>
+        <v>-25.22237055450141</v>
       </c>
       <c r="F92">
-        <v>0.2682268747509035</v>
+        <v>0.4784685861432365</v>
       </c>
       <c r="G92">
-        <v>-4.131753995320053</v>
+        <v>-3.793667842667523</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.811046945854662</v>
       </c>
       <c r="E93">
-        <v>-26.74899159807121</v>
+        <v>-27.20313867087845</v>
       </c>
       <c r="F93">
-        <v>0.2283531190649268</v>
+        <v>0.01837509470751454</v>
       </c>
       <c r="G93">
-        <v>-4.004096048780217</v>
+        <v>-2.61847383440934</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.473738089735067</v>
       </c>
       <c r="E94">
-        <v>-29.30062367632918</v>
+        <v>-29.69968412707011</v>
       </c>
       <c r="F94">
-        <v>0.1660247890568919</v>
+        <v>0.2581885548058906</v>
       </c>
       <c r="G94">
-        <v>-3.726006912935898</v>
+        <v>-3.496778118705682</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.12068472586444</v>
       </c>
       <c r="E95">
-        <v>-31.12014189024109</v>
+        <v>-32.74888681539487</v>
       </c>
       <c r="F95">
-        <v>0.4085669744475702</v>
+        <v>0.1088846796278367</v>
       </c>
       <c r="G95">
-        <v>-4.23810527076914</v>
+        <v>-2.914830560539357</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.755360966685828</v>
       </c>
       <c r="E96">
-        <v>-34.18592105767092</v>
+        <v>-33.67595375000814</v>
       </c>
       <c r="F96">
-        <v>0.1067134188177692</v>
+        <v>0.335458358273139</v>
       </c>
       <c r="G96">
-        <v>-3.95538799226092</v>
+        <v>-3.246500875936781</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.38170063150559</v>
       </c>
       <c r="E97">
-        <v>-36.37583448185521</v>
+        <v>-36.32377288042603</v>
       </c>
       <c r="F97">
-        <v>0.07179032782345622</v>
+        <v>-0.2642902800508221</v>
       </c>
       <c r="G97">
-        <v>-3.950101051034704</v>
+        <v>-3.839025627101077</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.007051105848618</v>
       </c>
       <c r="E98">
-        <v>-38.80256445427062</v>
+        <v>-39.09802926937508</v>
       </c>
       <c r="F98">
-        <v>-0.003296337039358862</v>
+        <v>0.2031999098629598</v>
       </c>
       <c r="G98">
-        <v>-3.385825184957008</v>
+        <v>-3.955907747910585</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.647562014119925</v>
       </c>
       <c r="E99">
-        <v>-41.75462684665685</v>
+        <v>-41.34766873724654</v>
       </c>
       <c r="F99">
-        <v>-0.2097316112639331</v>
+        <v>0.1123189459054671</v>
       </c>
       <c r="G99">
-        <v>-4.384308893419973</v>
+        <v>-3.214825576217034</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.295440340093721</v>
       </c>
       <c r="E100">
-        <v>-42.83550566517764</v>
+        <v>-44.90236912938851</v>
       </c>
       <c r="F100">
-        <v>-0.1551879876832408</v>
+        <v>-0.1411135932127305</v>
       </c>
       <c r="G100">
-        <v>-4.176899904839094</v>
+        <v>-3.801450935230349</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.975701628604324</v>
       </c>
       <c r="E101">
-        <v>-45.63516452907272</v>
+        <v>-47.01000244509044</v>
       </c>
       <c r="F101">
-        <v>-0.1755892872859318</v>
+        <v>-0.09690048331844968</v>
       </c>
       <c r="G101">
-        <v>-5.065622475947523</v>
+        <v>-3.915601855969959</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.65680891335734</v>
       </c>
       <c r="E102">
-        <v>-48.5560857378267</v>
+        <v>-49.52757473821821</v>
       </c>
       <c r="F102">
-        <v>-0.2167529714400339</v>
+        <v>0.06214080768068367</v>
       </c>
       <c r="G102">
-        <v>-4.171748695979988</v>
+        <v>-3.407505947693696</v>
       </c>
     </row>
   </sheetData>
